--- a/converted_files/835/claim_adj_reason.xlsx
+++ b/converted_files/835/claim_adj_reason.xlsx
@@ -1107,7 +1107,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f4de2</t>
+          <t>69e82c67836d7d05c9a029e6</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -1569,7 +1569,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f4de2</t>
+          <t>69e82c67836d7d05c9a029e6</t>
         </is>
       </c>
       <c r="B3"/>
@@ -1821,7 +1821,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f4de2</t>
+          <t>69e82c67836d7d05c9a029e6</t>
         </is>
       </c>
       <c r="B4"/>

--- a/converted_files/835/claim_adj_reason.xlsx
+++ b/converted_files/835/claim_adj_reason.xlsx
@@ -1107,7 +1107,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f4de2</t>
+          <t>69efef04ad4799caa7f5b833</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -1569,7 +1569,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f4de2</t>
+          <t>69efef04ad4799caa7f5b833</t>
         </is>
       </c>
       <c r="B3"/>
@@ -1821,7 +1821,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f4de2</t>
+          <t>69efef04ad4799caa7f5b833</t>
         </is>
       </c>
       <c r="B4"/>

--- a/converted_files/835/claim_adj_reason.xlsx
+++ b/converted_files/835/claim_adj_reason.xlsx
@@ -1107,7 +1107,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>69e82c67836d7d05c9a029e6</t>
+          <t>6a04cbecb80b363c8541f8a6</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -1569,7 +1569,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>69e82c67836d7d05c9a029e6</t>
+          <t>6a04cbecb80b363c8541f8a6</t>
         </is>
       </c>
       <c r="B3"/>
@@ -1821,7 +1821,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>69e82c67836d7d05c9a029e6</t>
+          <t>6a04cbecb80b363c8541f8a6</t>
         </is>
       </c>
       <c r="B4"/>

--- a/converted_files/835/claim_adj_reason.xlsx
+++ b/converted_files/835/claim_adj_reason.xlsx
@@ -1107,7 +1107,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a04cbecb80b363c8541f8a6</t>
+          <t>6a04cc5a1ef26d534baf152e</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -1569,7 +1569,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6a04cbecb80b363c8541f8a6</t>
+          <t>6a04cc5a1ef26d534baf152e</t>
         </is>
       </c>
       <c r="B3"/>
@@ -1821,7 +1821,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6a04cbecb80b363c8541f8a6</t>
+          <t>6a04cc5a1ef26d534baf152e</t>
         </is>
       </c>
       <c r="B4"/>

--- a/converted_files/835/claim_adj_reason.xlsx
+++ b/converted_files/835/claim_adj_reason.xlsx
@@ -1107,7 +1107,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf152e</t>
+          <t>6a32cb6297613a0e49906970</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -1569,7 +1569,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf152e</t>
+          <t>6a32cb6297613a0e49906970</t>
         </is>
       </c>
       <c r="B3"/>
@@ -1821,7 +1821,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf152e</t>
+          <t>6a32cb6297613a0e49906970</t>
         </is>
       </c>
       <c r="B4"/>

--- a/converted_files/835/claim_adj_reason.xlsx
+++ b/converted_files/835/claim_adj_reason.xlsx
@@ -6,7 +6,9 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Payments and Service Lines" r:id="rId3" sheetId="1"/>
+    <sheet name="Transactions" r:id="rId3" sheetId="1"/>
+    <sheet name="ProviderAdjustments" r:id="rId4" sheetId="2"/>
+    <sheet name="Service Lines" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
@@ -59,6 +61,733 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:AX2"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>TransactionType</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>FileName</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>TransactionControlNumber</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>TotalPaymentAmount</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>CreditOrDebitFlagCode</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>PaymentMethodType</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>ReceiverAccountNumber</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>PaymentDate</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>CheckOrEftTraceNumber</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>PayerEin</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>ProductionDate</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>PayerIdentificationType</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>PayerIdentifier</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>PayerName</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>PayerAddressLine</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>PayerAddressLine2</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>PayerAddressCity</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>PayerAddressStateCode</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>PayerAddressZipCode</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact1Name</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact1ContactNumber1Type</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact1ContactNumber1Number</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact1ContactNumber2Type</t>
+        </is>
+      </c>
+      <c r="Y1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact1ContactNumber2Number</t>
+        </is>
+      </c>
+      <c r="Z1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact2Name</t>
+        </is>
+      </c>
+      <c r="AA1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact2ContactNumber1Type</t>
+        </is>
+      </c>
+      <c r="AB1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact2ContactNumber1Number</t>
+        </is>
+      </c>
+      <c r="AC1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact2ContactNumber2Type</t>
+        </is>
+      </c>
+      <c r="AD1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact2ContactNumber2Number</t>
+        </is>
+      </c>
+      <c r="AE1" s="3" t="inlineStr">
+        <is>
+          <t>PayerAdditionalId1Type</t>
+        </is>
+      </c>
+      <c r="AF1" s="3" t="inlineStr">
+        <is>
+          <t>PayerAdditionalId1Identification</t>
+        </is>
+      </c>
+      <c r="AG1" s="3" t="inlineStr">
+        <is>
+          <t>PayerAdditionalId2Type</t>
+        </is>
+      </c>
+      <c r="AH1" s="3" t="inlineStr">
+        <is>
+          <t>PayerAdditionalId2Identification</t>
+        </is>
+      </c>
+      <c r="AI1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeIdentificationType</t>
+        </is>
+      </c>
+      <c r="AJ1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeIdentifier</t>
+        </is>
+      </c>
+      <c r="AK1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeTaxId</t>
+        </is>
+      </c>
+      <c r="AL1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeLastNameOrOrgName</t>
+        </is>
+      </c>
+      <c r="AM1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeAddressLine</t>
+        </is>
+      </c>
+      <c r="AN1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeAddressLine2</t>
+        </is>
+      </c>
+      <c r="AO1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeAddressCity</t>
+        </is>
+      </c>
+      <c r="AP1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeAddressStateCode</t>
+        </is>
+      </c>
+      <c r="AQ1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeAddressZipCode</t>
+        </is>
+      </c>
+      <c r="AR1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeAdditionalId1Type</t>
+        </is>
+      </c>
+      <c r="AS1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeAdditionalId1Identification</t>
+        </is>
+      </c>
+      <c r="AT1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeAdditionalId2Type</t>
+        </is>
+      </c>
+      <c r="AU1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeAdditionalId2Identification</t>
+        </is>
+      </c>
+      <c r="AV1" s="3" t="inlineStr">
+        <is>
+          <t>RemittanceDeliveryMethodReportTransmissionCode</t>
+        </is>
+      </c>
+      <c r="AW1" s="3" t="inlineStr">
+        <is>
+          <t>RemittanceDeliveryMethodName</t>
+        </is>
+      </c>
+      <c r="AX1" s="3" t="inlineStr">
+        <is>
+          <t>RemittanceDeliveryMethodCommunicationNumber</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>6a68fd29aa71f5c1ede918ce</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>835</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>claim_adj_reason.dat</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>10060875</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>80.0</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="H2"/>
+      <c r="I2" s="4" t="n">
+        <v>43693.0</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>CK NUMBER 1</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>1234567890</t>
+        </is>
+      </c>
+      <c r="L2" s="4" t="n">
+        <v>43704.0</v>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>PAYOR_ID</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>1234567890</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>ANY PLAN USA</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="inlineStr">
+        <is>
+          <t>1 WALK THIS WAY</t>
+        </is>
+      </c>
+      <c r="Q2"/>
+      <c r="R2" s="3" t="inlineStr">
+        <is>
+          <t>ANYCITY</t>
+        </is>
+      </c>
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>45209</t>
+        </is>
+      </c>
+      <c r="U2"/>
+      <c r="V2" s="3" t="inlineStr">
+        <is>
+          <t>PHONE</t>
+        </is>
+      </c>
+      <c r="W2" s="3" t="inlineStr">
+        <is>
+          <t>8661112222</t>
+        </is>
+      </c>
+      <c r="X2"/>
+      <c r="Y2"/>
+      <c r="Z2" s="3" t="inlineStr">
+        <is>
+          <t>EDI</t>
+        </is>
+      </c>
+      <c r="AA2" s="3" t="inlineStr">
+        <is>
+          <t>PHONE</t>
+        </is>
+      </c>
+      <c r="AB2" s="3" t="inlineStr">
+        <is>
+          <t>8002223333</t>
+        </is>
+      </c>
+      <c r="AC2" s="3" t="inlineStr">
+        <is>
+          <t>EMAIL</t>
+        </is>
+      </c>
+      <c r="AD2" s="3" t="inlineStr">
+        <is>
+          <t>EDI.SUPPORT@ANYPAYER.COM</t>
+        </is>
+      </c>
+      <c r="AE2"/>
+      <c r="AF2"/>
+      <c r="AG2"/>
+      <c r="AH2"/>
+      <c r="AI2" s="3" t="inlineStr">
+        <is>
+          <t>NPI</t>
+        </is>
+      </c>
+      <c r="AJ2" s="3" t="inlineStr">
+        <is>
+          <t>1123454567</t>
+        </is>
+      </c>
+      <c r="AK2" s="3" t="inlineStr">
+        <is>
+          <t>123456789</t>
+        </is>
+      </c>
+      <c r="AL2" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER</t>
+        </is>
+      </c>
+      <c r="AM2" s="3" t="inlineStr">
+        <is>
+          <t>2255 ANY ROAD</t>
+        </is>
+      </c>
+      <c r="AN2"/>
+      <c r="AO2" s="3" t="inlineStr">
+        <is>
+          <t>ANY CITY</t>
+        </is>
+      </c>
+      <c r="AP2" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="AQ2" s="3" t="inlineStr">
+        <is>
+          <t>12211</t>
+        </is>
+      </c>
+      <c r="AR2"/>
+      <c r="AS2"/>
+      <c r="AT2"/>
+      <c r="AU2"/>
+      <c r="AV2"/>
+      <c r="AW2"/>
+      <c r="AX2"/>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:BC1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>TransactionType</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>FileName</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>TransactionControlNumber</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>TotalPaymentAmount</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>CreditOrDebitFlagCode</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>PaymentMethodType</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>ReceiverAccountNumber</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>PaymentDate</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>CheckOrEftTraceNumber</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>PayerEin</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>ProductionDate</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>PayerIdentificationType</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>PayerIdentifier</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>PayerName</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>PayerAddressLine</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>PayerAddressLine2</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>PayerAddressCity</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>PayerAddressStateCode</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>PayerAddressZipCode</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact1Name</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact1ContactNumber1Type</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact1ContactNumber1Number</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact1ContactNumber2Type</t>
+        </is>
+      </c>
+      <c r="Y1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact1ContactNumber2Number</t>
+        </is>
+      </c>
+      <c r="Z1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact2Name</t>
+        </is>
+      </c>
+      <c r="AA1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact2ContactNumber1Type</t>
+        </is>
+      </c>
+      <c r="AB1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact2ContactNumber1Number</t>
+        </is>
+      </c>
+      <c r="AC1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact2ContactNumber2Type</t>
+        </is>
+      </c>
+      <c r="AD1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact2ContactNumber2Number</t>
+        </is>
+      </c>
+      <c r="AE1" s="3" t="inlineStr">
+        <is>
+          <t>PayerAdditionalId1Type</t>
+        </is>
+      </c>
+      <c r="AF1" s="3" t="inlineStr">
+        <is>
+          <t>PayerAdditionalId1Identification</t>
+        </is>
+      </c>
+      <c r="AG1" s="3" t="inlineStr">
+        <is>
+          <t>PayerAdditionalId2Type</t>
+        </is>
+      </c>
+      <c r="AH1" s="3" t="inlineStr">
+        <is>
+          <t>PayerAdditionalId2Identification</t>
+        </is>
+      </c>
+      <c r="AI1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeIdentificationType</t>
+        </is>
+      </c>
+      <c r="AJ1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeIdentifier</t>
+        </is>
+      </c>
+      <c r="AK1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeTaxId</t>
+        </is>
+      </c>
+      <c r="AL1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeLastNameOrOrgName</t>
+        </is>
+      </c>
+      <c r="AM1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeAddressLine</t>
+        </is>
+      </c>
+      <c r="AN1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeAddressLine2</t>
+        </is>
+      </c>
+      <c r="AO1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeAddressCity</t>
+        </is>
+      </c>
+      <c r="AP1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeAddressStateCode</t>
+        </is>
+      </c>
+      <c r="AQ1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeAddressZipCode</t>
+        </is>
+      </c>
+      <c r="AR1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeAdditionalId1Type</t>
+        </is>
+      </c>
+      <c r="AS1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeAdditionalId1Identification</t>
+        </is>
+      </c>
+      <c r="AT1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeAdditionalId2Type</t>
+        </is>
+      </c>
+      <c r="AU1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeAdditionalId2Identification</t>
+        </is>
+      </c>
+      <c r="AV1" s="3" t="inlineStr">
+        <is>
+          <t>RemittanceDeliveryMethodReportTransmissionCode</t>
+        </is>
+      </c>
+      <c r="AW1" s="3" t="inlineStr">
+        <is>
+          <t>RemittanceDeliveryMethodName</t>
+        </is>
+      </c>
+      <c r="AX1" s="3" t="inlineStr">
+        <is>
+          <t>RemittanceDeliveryMethodCommunicationNumber</t>
+        </is>
+      </c>
+      <c r="AY1" s="3" t="inlineStr">
+        <is>
+          <t>ProviderIdentifier</t>
+        </is>
+      </c>
+      <c r="AZ1" s="3" t="inlineStr">
+        <is>
+          <t>FiscalPeriodDate</t>
+        </is>
+      </c>
+      <c r="BA1" s="3" t="inlineStr">
+        <is>
+          <t>ProviderAdjustmentReason</t>
+        </is>
+      </c>
+      <c r="BB1" s="3" t="inlineStr">
+        <is>
+          <t>ProviderAdjustmentReferenceIdentification</t>
+        </is>
+      </c>
+      <c r="BC1" s="3" t="inlineStr">
+        <is>
+          <t>ProviderAdjustmentAmount</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:GZ4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
@@ -410,37 +1139,37 @@
       </c>
       <c r="BR1" s="3" t="inlineStr">
         <is>
+          <t>PayeeTaxId</t>
+        </is>
+      </c>
+      <c r="BS1" s="3" t="inlineStr">
+        <is>
           <t>PayeeLastNameOrOrgName</t>
         </is>
       </c>
-      <c r="BS1" s="3" t="inlineStr">
+      <c r="BT1" s="3" t="inlineStr">
         <is>
           <t>PayeeAddressLine</t>
         </is>
       </c>
-      <c r="BT1" s="3" t="inlineStr">
+      <c r="BU1" s="3" t="inlineStr">
         <is>
           <t>PayeeAddressLine2</t>
         </is>
       </c>
-      <c r="BU1" s="3" t="inlineStr">
+      <c r="BV1" s="3" t="inlineStr">
         <is>
           <t>PayeeAddressCity</t>
         </is>
       </c>
-      <c r="BV1" s="3" t="inlineStr">
+      <c r="BW1" s="3" t="inlineStr">
         <is>
           <t>PayeeAddressStateCode</t>
         </is>
       </c>
-      <c r="BW1" s="3" t="inlineStr">
+      <c r="BX1" s="3" t="inlineStr">
         <is>
           <t>PayeeAddressZipCode</t>
-        </is>
-      </c>
-      <c r="BX1" s="3" t="inlineStr">
-        <is>
-          <t>PayeeContacts</t>
         </is>
       </c>
       <c r="BY1" s="3" t="inlineStr">
@@ -1107,7 +1836,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a32cb6297613a0e49906970</t>
+          <t>6a68fd29aa71f5c1ede91900</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -1308,31 +2037,35 @@
       </c>
       <c r="BR2" s="3" t="inlineStr">
         <is>
+          <t>123456789</t>
+        </is>
+      </c>
+      <c r="BS2" s="3" t="inlineStr">
+        <is>
           <t>PROVIDER</t>
         </is>
       </c>
-      <c r="BS2" s="3" t="inlineStr">
+      <c r="BT2" s="3" t="inlineStr">
         <is>
           <t>2255 ANY ROAD</t>
         </is>
       </c>
-      <c r="BT2"/>
-      <c r="BU2" s="3" t="inlineStr">
+      <c r="BU2"/>
+      <c r="BV2" s="3" t="inlineStr">
         <is>
           <t>ANY CITY</t>
         </is>
       </c>
-      <c r="BV2" s="3" t="inlineStr">
+      <c r="BW2" s="3" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="BW2" s="3" t="inlineStr">
+      <c r="BX2" s="3" t="inlineStr">
         <is>
           <t>12211</t>
         </is>
       </c>
-      <c r="BX2"/>
       <c r="BY2"/>
       <c r="BZ2"/>
       <c r="CA2"/>
@@ -1569,7 +2302,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6a32cb6297613a0e49906970</t>
+          <t>6a68fd29aa71f5c1ede91900</t>
         </is>
       </c>
       <c r="B3"/>
@@ -1821,7 +2554,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6a32cb6297613a0e49906970</t>
+          <t>6a68fd29aa71f5c1ede91900</t>
         </is>
       </c>
       <c r="B4"/>
